--- a/artfynd/A 64110-2025 artfynd.xlsx
+++ b/artfynd/A 64110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130806125</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130807523</v>
       </c>
       <c r="B3" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130807513</v>
       </c>
       <c r="B4" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130806161</v>
       </c>
       <c r="B5" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130806143</v>
       </c>
       <c r="B6" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130807263</v>
       </c>
       <c r="B7" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130807391</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130806878</v>
+        <v>130806196</v>
       </c>
       <c r="B9" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472144</v>
+        <v>472131</v>
       </c>
       <c r="R9" t="n">
-        <v>6864413</v>
+        <v>6864526</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130806196</v>
+        <v>130806878</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472131</v>
+        <v>472144</v>
       </c>
       <c r="R10" t="n">
-        <v>6864526</v>
+        <v>6864413</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1545,6 +1545,976 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130839116</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>472175</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6864536</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130839125</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>472181</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6864563</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130839368</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>472174</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6864517</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130839206</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>472147</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6864552</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130839718</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79288</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>637</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>472147</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6864379</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130839483</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>472187</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6864484</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130839512</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>472160</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6864466</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130839325</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>472165</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6864516</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130839361</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>472176</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6864518</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130839096</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>472178</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6864559</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64110-2025 artfynd.xlsx
+++ b/artfynd/A 64110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130806196</v>
+        <v>130806878</v>
       </c>
       <c r="B9" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472131</v>
+        <v>472144</v>
       </c>
       <c r="R9" t="n">
-        <v>6864526</v>
+        <v>6864413</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130806878</v>
+        <v>130806196</v>
       </c>
       <c r="B10" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472144</v>
+        <v>472131</v>
       </c>
       <c r="R10" t="n">
-        <v>6864413</v>
+        <v>6864526</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130839718</v>
+        <v>130839483</v>
       </c>
       <c r="B15" t="n">
-        <v>79288</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>637</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472147</v>
+        <v>472187</v>
       </c>
       <c r="R15" t="n">
-        <v>6864379</v>
+        <v>6864484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130839483</v>
+        <v>130839512</v>
       </c>
       <c r="B16" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472187</v>
+        <v>472160</v>
       </c>
       <c r="R16" t="n">
-        <v>6864484</v>
+        <v>6864466</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130839512</v>
+        <v>130839325</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,34 +2141,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472160</v>
+        <v>472165</v>
       </c>
       <c r="R17" t="n">
-        <v>6864466</v>
+        <v>6864516</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130839325</v>
+        <v>130839361</v>
       </c>
       <c r="B18" t="n">
         <v>80326</v>
@@ -2258,14 +2258,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472165</v>
+        <v>472176</v>
       </c>
       <c r="R18" t="n">
-        <v>6864516</v>
+        <v>6864518</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130839361</v>
+        <v>130839096</v>
       </c>
       <c r="B19" t="n">
         <v>80326</v>
@@ -2355,17 +2355,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472176</v>
+        <v>472178</v>
       </c>
       <c r="R19" t="n">
-        <v>6864518</v>
+        <v>6864559</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2418,103 +2418,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>130839096</v>
-      </c>
-      <c r="B20" t="n">
-        <v>80326</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>472178</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6864559</v>
-      </c>
-      <c r="S20" t="n">
-        <v>20</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Sveg</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>lennart karlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64110-2025 artfynd.xlsx
+++ b/artfynd/A 64110-2025 artfynd.xlsx
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130839368</v>
+        <v>130839206</v>
       </c>
       <c r="B13" t="n">
-        <v>80327</v>
+        <v>80326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472174</v>
+        <v>472147</v>
       </c>
       <c r="R13" t="n">
-        <v>6864517</v>
+        <v>6864552</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130839206</v>
+        <v>130839368</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472147</v>
+        <v>472174</v>
       </c>
       <c r="R14" t="n">
-        <v>6864552</v>
+        <v>6864517</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 64110-2025 artfynd.xlsx
+++ b/artfynd/A 64110-2025 artfynd.xlsx
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130839206</v>
+        <v>130839368</v>
       </c>
       <c r="B13" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472147</v>
+        <v>472174</v>
       </c>
       <c r="R13" t="n">
-        <v>6864552</v>
+        <v>6864517</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130839368</v>
+        <v>130839206</v>
       </c>
       <c r="B14" t="n">
-        <v>80327</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472174</v>
+        <v>472147</v>
       </c>
       <c r="R14" t="n">
-        <v>6864517</v>
+        <v>6864552</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 64110-2025 artfynd.xlsx
+++ b/artfynd/A 64110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130805864</v>
+        <v>130806125</v>
       </c>
       <c r="B2" t="n">
-        <v>80349</v>
+        <v>79244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472085</v>
+        <v>472170</v>
       </c>
       <c r="R2" t="n">
-        <v>6864708</v>
+        <v>6864573</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130805606</v>
+        <v>130807523</v>
       </c>
       <c r="B3" t="n">
         <v>80349</v>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472103</v>
+        <v>472102</v>
       </c>
       <c r="R3" t="n">
-        <v>6864732</v>
+        <v>6864255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130805735</v>
+        <v>130807513</v>
       </c>
       <c r="B4" t="n">
-        <v>79323</v>
+        <v>80350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472075</v>
+        <v>472101</v>
       </c>
       <c r="R4" t="n">
-        <v>6864781</v>
+        <v>6864261</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På björkstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130805965</v>
+        <v>130806161</v>
       </c>
       <c r="B5" t="n">
         <v>80349</v>
@@ -1007,14 +997,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472083</v>
+        <v>472150</v>
       </c>
       <c r="R5" t="n">
-        <v>6864712</v>
+        <v>6864539</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på björk av naturvärdeskvalitet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130805806</v>
+        <v>130806143</v>
       </c>
       <c r="B6" t="n">
         <v>80349</v>
@@ -1109,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472000</v>
+        <v>472165</v>
       </c>
       <c r="R6" t="n">
-        <v>6864709</v>
+        <v>6864552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,11 +1136,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1177,6 +1157,1267 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130807263</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80350</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>472117</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6864351</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130807391</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>472139</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6864315</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130806878</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80349</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>472144</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6864413</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130806196</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>472131</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6864526</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130839116</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>472175</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6864536</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130839125</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80349</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>472181</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6864563</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130839206</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80349</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>472147</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6864552</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130839368</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80350</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>472174</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6864517</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130839483</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80349</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>472187</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6864484</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130839512</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>472160</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6864466</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130839325</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80349</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>472165</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6864516</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130839361</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80349</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kristinehamnskojan, Kristinehamnskojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>472176</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6864518</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130839096</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80349</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öratjärnknallarna, Öratjärnknallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>472178</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6864559</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
